--- a/Results/Classifying images into unsuitable categories (Responses).xlsx
+++ b/Results/Classifying images into unsuitable categories (Responses).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ameli\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ameli\Documents\EMC\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B39E75A-2E20-4878-ADCE-9C43297A3670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8974265F-E88D-4FD3-A435-19555879C6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -617,22 +617,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
@@ -656,13 +640,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form responses 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
